--- a/data/merged/2026-09-23/MERGED_IT_Spot-Cleaner_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_IT_Spot-Cleaner_2026-09-23.xlsx
@@ -3468,13 +3468,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3512,13 +3512,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3556,13 +3556,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3694,7 +3694,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3732,13 +3732,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3782,7 +3782,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3820,13 +3820,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3864,13 +3864,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3952,13 +3952,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4046,7 +4046,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4134,7 +4134,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4260,13 +4260,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4348,13 +4348,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4530,7 +4530,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4618,7 +4618,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4832,13 +4832,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4876,13 +4876,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4920,13 +4920,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4964,13 +4964,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5272,13 +5272,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5316,13 +5316,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5360,13 +5360,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5404,13 +5404,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5427,94 +5427,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5856,7 +5768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6271,7 +6183,7 @@
       <c r="B2" s="13"/>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B07GXS35PG</t>
         </is>
       </c>
       <c r="D2" s="14"/>
@@ -6284,23 +6196,23 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Potenziatore Detergente 1 L 1134NsPer formule detergenti per pulitori portatili SpotClean, per moquett</t>
+          <t>BISSELL SpotClean ProHeat Lavatappeti 330W 36988sPulitore macchie con tecnologia HeatWave, lava tappezzeria per tappeti, au</t>
         </is>
       </c>
       <c r="I2" s="14"/>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.it/dp/B07GXS35PG?psc=1</t>
         </is>
       </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51L21EY2IeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71PEgi0LW+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B07GXS35PG</t>
         </is>
       </c>
       <c r="M2" s="1"/>
@@ -6316,16 +6228,18 @@
       <c r="W2" s="15"/>
       <c r="X2" s="15"/>
       <c r="Y2"/>
-      <c r="Z2" s="4"/>
+      <c r="Z2" s="4">
+        <v>122.94</v>
+      </c>
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
       <c r="AD2" s="19">
-        <v>9405</v>
+        <v>23989</v>
       </c>
       <c r="AE2"/>
       <c r="AF2" s="20">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG2" s="21">
         <v>0</v>
@@ -6377,7 +6291,7 @@
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>B07GXS35PG</t>
+          <t>B084PSXMQM</t>
         </is>
       </c>
       <c r="D3" s="14"/>
@@ -6390,23 +6304,23 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean ProHeat Lavatappeti 330W 36988sPulitore macchie con tecnologia HeatWave, lava tappezzeria per tappeti, au</t>
+          <t>BISSELL SpotClean Pet Pro Lavatappeti 750W 15585sPulitore e lava tappezzeria per tappeti, auto, divani, moquette, materassi</t>
         </is>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B07GXS35PG?psc=1</t>
+          <t>https://www.amazon.it/dp/B084PSXMQM?psc=1</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71PEgi0LW+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>B07GXS35PG</t>
+          <t>B084PSXMQM</t>
         </is>
       </c>
       <c r="M3" s="1"/>
@@ -6422,18 +6336,16 @@
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3"/>
-      <c r="Z3" s="4">
-        <v>122.94</v>
-      </c>
+      <c r="Z3" s="4"/>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3" s="19">
-        <v>23989</v>
+        <v>20947</v>
       </c>
       <c r="AE3"/>
       <c r="AF3" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG3" s="21">
         <v>0</v>
@@ -6485,7 +6397,7 @@
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>B084PSXMQM</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="D4" s="14"/>
@@ -6498,23 +6410,23 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean Pet Pro Lavatappeti 750W 15585sPulitore e lava tappezzeria per tappeti, auto, divani, moquette, materassi</t>
+          <t>HAUSHOF StainZapper - Lavatappeti Portatile, Lava Divano ad Acqua 400WsLava Tappezzeria Ideale per Pulisci Scale, divano, S</t>
         </is>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B084PSXMQM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0B3J3Q9RD?psc=1</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>B084PSXMQM</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="M4" s="1"/>
@@ -6530,16 +6442,18 @@
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
       <c r="Y4"/>
-      <c r="Z4" s="4"/>
+      <c r="Z4" s="4">
+        <v>81.14</v>
+      </c>
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
       <c r="AD4" s="19">
-        <v>20947</v>
+        <v>4904</v>
       </c>
       <c r="AE4"/>
       <c r="AF4" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG4" s="21">
         <v>0</v>
@@ -6591,7 +6505,7 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0BMF3LFC8</t>
         </is>
       </c>
       <c r="D5" s="14"/>
@@ -6604,23 +6518,23 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>STANHOMEsDetergente Smacchiante Tappeti Carpet Cleaner, 500 ML, Pulisce e Smacchia i Tessuti d'Arredamento</t>
+          <t>Vacmaster SCA0801 Lavatappeti Detergente per Tappezzeria &amp; MacchiesAspirapolvere umido e secco Potenza detergente Per divan</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B086Q46MMD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BMF3LFC8?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61sF4ZQ-2cL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0BMF3LFC8</t>
         </is>
       </c>
       <c r="M5" s="1"/>
@@ -6641,7 +6555,7 @@
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5" s="19">
-        <v>74</v>
+        <v>3882</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" s="20">
@@ -6697,7 +6611,7 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0BPZJSXCQ</t>
         </is>
       </c>
       <c r="D6" s="14"/>
@@ -6710,23 +6624,23 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper - Lavatappeti Portatile, Lava Divano ad Acqua 400WsLava Tappezzeria Ideale per Pulisci Scale, divano, S</t>
+          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
         </is>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51lbQJ889kL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0BPZJSXCQ</t>
         </is>
       </c>
       <c r="M6" s="1"/>
@@ -6743,13 +6657,13 @@
       <c r="X6" s="15"/>
       <c r="Y6"/>
       <c r="Z6" s="4">
-        <v>81.14</v>
+        <v>72.53</v>
       </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6" s="19">
-        <v>4904</v>
+        <v>3295</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" s="20">
@@ -6805,7 +6719,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B0BMF3LFC8</t>
+          <t>B0BS13X4Z2</t>
         </is>
       </c>
       <c r="D7" s="14"/>
@@ -6818,23 +6732,23 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster SCA0801 Lavatappeti Detergente per Tappezzeria &amp; MacchiesAspirapolvere umido e secco Potenza detergente Per divan</t>
+          <t>KÄRCHER lavatappeti e lavamoquette Puzzi 8/1, per tappezzeria e superfici tessili, serbatoio: 8 l, pressione spruzzo: 1 bar:</t>
         </is>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BMF3LFC8?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BS13X4Z2?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B0BMF3LFC8</t>
+          <t>B0BS13X4Z2</t>
         </is>
       </c>
       <c r="M7" s="1"/>
@@ -6855,11 +6769,11 @@
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7" s="19">
-        <v>3882</v>
+        <v>1248</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG7" s="21">
         <v>0</v>
@@ -6911,7 +6825,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
+          <t>B0BY2ZPQ1N</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -6924,23 +6838,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
+          <t>BISSELL Naturale detergente per pulizia profonda della moquette, 1,75 L, rimuove lo sporco ostinato degli animali domestici,</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51lbQJ889kL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
+          <t>B0BY2ZPQ1N</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -6956,18 +6870,16 @@
       <c r="W8" s="15"/>
       <c r="X8" s="15"/>
       <c r="Y8"/>
-      <c r="Z8" s="4">
-        <v>72.53</v>
-      </c>
+      <c r="Z8" s="4"/>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="19">
-        <v>3295</v>
+        <v>75</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG8" s="21">
         <v>0</v>
@@ -7019,7 +6931,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B0BS13X4Z2</t>
+          <t>B0CM6TD52F</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -7032,23 +6944,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER lavatappeti e lavamoquette Puzzi 8/1, per tappezzeria e superfici tessili, serbatoio: 8 l, pressione spruzzo: 1 bar:</t>
+          <t>LEHMANN Ultrawash Aspirapolvere per Lavaggio 4 in 1sAspirapolvere per tappeti e mobili imbottiti | Aspirapolvere senza sacc</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BS13X4Z2?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CM6TD52F?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71csw3LJPeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B0BS13X4Z2</t>
+          <t>B0CM6TD52F</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -7069,11 +6981,11 @@
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="19">
-        <v>1248</v>
+        <v>361</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="20">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG9" s="21">
         <v>0</v>
@@ -7125,7 +7037,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0BY2ZPQ1N</t>
+          <t>B0CW9VBM8R</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -7138,23 +7050,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Naturale detergente per pulizia profonda della moquette, 1,75 L, rimuove lo sporco ostinato degli animali domestici,</t>
+          <t>BISSELL SpotClean C5, Lavatrice portatile per tessuti e imbottiti con sistema a tripla azione, ideale per tappeti, divani, in</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CW9VBM8R?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71FFs6EAy4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0BY2ZPQ1N</t>
+          <t>B0CW9VBM8R</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7175,11 +7087,11 @@
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="19">
-        <v>75</v>
+        <v>4726</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG10" s="21">
         <v>0</v>
@@ -7231,7 +7143,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0CM6TD52F</t>
+          <t>B0CXJLJQD1</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -7244,23 +7156,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN Ultrawash Aspirapolvere per Lavaggio 4 in 1sAspirapolvere per tappeti e mobili imbottiti | Aspirapolvere senza sacc</t>
+          <t>BISSELL SpotClean ProHeat Advanced Lavatappeti 1125W 3924NsPulitore per tappeti e tappezzeria, pulizia tripla macchie ostin</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CM6TD52F?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CXJLJQD1?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71csw3LJPeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61MZMklEU5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0CM6TD52F</t>
+          <t>B0CXJLJQD1</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7276,16 +7188,18 @@
       <c r="W11" s="15"/>
       <c r="X11" s="15"/>
       <c r="Y11"/>
-      <c r="Z11" s="4"/>
+      <c r="Z11" s="4">
+        <v>147.53</v>
+      </c>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="19">
-        <v>361</v>
+        <v>732</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="20">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG11" s="21">
         <v>0</v>
@@ -7337,7 +7251,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0CW9VBM8R</t>
+          <t>B0CXMC73YV</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -7350,23 +7264,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean C5, Lavatrice portatile per tessuti e imbottiti con sistema a tripla azione, ideale per tappeti, divani, in</t>
+          <t>Shark StainStriker, Pulitore Tappezzeria e Smacchiatore, 5 Accessori, 450WsPeli di Animali Domestici, Tubo Flessibile, 2 De</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CW9VBM8R?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CXMC73YV?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71FFs6EAy4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71sPYtqS0TL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0CW9VBM8R</t>
+          <t>B0CXMC73YV</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7382,12 +7296,14 @@
       <c r="W12" s="15"/>
       <c r="X12" s="15"/>
       <c r="Y12"/>
-      <c r="Z12" s="4"/>
+      <c r="Z12" s="4">
+        <v>107.02</v>
+      </c>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="19">
-        <v>4726</v>
+        <v>593</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="20">
@@ -7443,7 +7359,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0CXJLJQD1</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -7456,23 +7372,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean ProHeat Advanced Lavatappeti 1125W 3924NsPulitore per tappeti e tappezzeria, pulizia tripla macchie ostin</t>
+          <t>HAUSHOF StainZapper Pro - Lavatappeti Portatile 450W 11,5kPas1,5L lava tappezzeria ad Acqua con Detergente e Spazzola per G</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CXJLJQD1?psc=1</t>
+          <t>https://www.amazon.it/dp/B0D2HFLM1C?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61MZMklEU5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0CXJLJQD1</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7488,18 +7404,16 @@
       <c r="W13" s="15"/>
       <c r="X13" s="15"/>
       <c r="Y13"/>
-      <c r="Z13" s="4">
-        <v>147.53</v>
-      </c>
+      <c r="Z13" s="4"/>
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="19">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG13" s="21">
         <v>0</v>
@@ -7551,7 +7465,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0CXMC73YV</t>
+          <t>B0D6YR6562</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7564,23 +7478,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker, Pulitore Tappezzeria e Smacchiatore, 5 Accessori, 450WsPeli di Animali Domestici, Tubo Flessibile, 2 De</t>
+          <t>Vacmaster SCB0501 Lavatappeti Aspirapolvere Tessuti Lava Tappezzeria Asciuga e Aspira Acqua Pulitore a Vapore per Divano Tapp</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CXMC73YV?psc=1</t>
+          <t>https://www.amazon.it/dp/B0D6YR6562?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71sPYtqS0TL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71TZUWy-CyL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0CXMC73YV</t>
+          <t>B0D6YR6562</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7597,17 +7511,17 @@
       <c r="X14" s="15"/>
       <c r="Y14"/>
       <c r="Z14" s="4">
-        <v>107.02</v>
+        <v>65.57</v>
       </c>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="19">
-        <v>593</v>
+        <v>2042</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="20">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG14" s="21">
         <v>0</v>
@@ -7659,7 +7573,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0D8KZDB13</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7672,23 +7586,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Pro - Lavatappeti Portatile 450W 11,5kPas1,5L lava tappezzeria ad Acqua con Detergente e Spazzola per G</t>
+          <t>WORKPRO Lavatappeti Portatile 450W, Lava Tappezzeria, Pulitore Tappezzeria, Ideale per Pulisci Scale, Divano, Sedili Auto, Mo</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0D2HFLM1C?psc=1</t>
+          <t>https://www.amazon.it/dp/B0D8KZDB13?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71xvnovCAAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0D8KZDB13</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7709,11 +7623,11 @@
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="19">
-        <v>740</v>
+        <v>210</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG15" s="21">
         <v>0</v>
@@ -7765,7 +7679,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0D6YR6562</t>
+          <t>B0DBLD211L</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7778,23 +7692,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster SCB0501 Lavatappeti Aspirapolvere Tessuti Lava Tappezzeria Asciuga e Aspira Acqua Pulitore a Vapore per Divano Tapp</t>
+          <t>KÄRCHER Lavatappeti Smacchiatore SE 3 Compact, serbatoio acqua pulita: 1,7 l, peso: 4,1 kg, per Tessuti, Moquette, Auto Tappe</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0D6YR6562?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DBLD211L?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71TZUWy-CyL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61v4meZXpjL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0D6YR6562</t>
+          <t>B0DBLD211L</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7810,18 +7724,16 @@
       <c r="W16" s="15"/>
       <c r="X16" s="15"/>
       <c r="Y16"/>
-      <c r="Z16" s="4">
-        <v>65.57</v>
-      </c>
+      <c r="Z16" s="4"/>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="19">
-        <v>2042</v>
+        <v>1007</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="20">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG16" s="21">
         <v>0</v>
@@ -7873,7 +7785,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0D8KZDB13</t>
+          <t>B0DD49JNRL</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7886,23 +7798,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>WORKPRO Lavatappeti Portatile 450W, Lava Tappezzeria, Pulitore Tappezzeria, Ideale per Pulisci Scale, Divano, Sedili Auto, Mo</t>
+          <t>Rowenta Clean It, Lavatappeti Portatile, Blu, IN5020sLava Tappezzeria, Divani e Auto, Testine Intercambiabili, Doppio Serba</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0D8KZDB13?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DD49JNRL?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71xvnovCAAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71eADlcR+FL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0D8KZDB13</t>
+          <t>B0DD49JNRL</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7918,16 +7830,18 @@
       <c r="W17" s="15"/>
       <c r="X17" s="15"/>
       <c r="Y17"/>
-      <c r="Z17" s="4"/>
+      <c r="Z17" s="4">
+        <v>147.53</v>
+      </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="19">
-        <v>210</v>
+        <v>1798</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG17" s="21">
         <v>0</v>
@@ -7979,7 +7893,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0DBLD211L</t>
+          <t>B0DDKZBYK6</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -7992,23 +7906,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER Lavatappeti Smacchiatore SE 3 Compact, serbatoio acqua pulita: 1,7 l, peso: 4,1 kg, per Tessuti, Moquette, Auto Tappe</t>
+          <t>Rivenara Lavatappeti Aspirapolvere Tessuti Divani- 450 W Lava Tappezzeria Asciuga e Aspira Acqua Pulitore per Divano Tappeti</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DBLD211L?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DDKZBYK6?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61v4meZXpjL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0DBLD211L</t>
+          <t>B0DDKZBYK6</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8029,7 +7943,7 @@
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="19">
-        <v>1007</v>
+        <v>3801</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="20">
@@ -8085,7 +7999,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0DD49JNRL</t>
+          <t>B0DFLYY2H7</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8098,23 +8012,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Rowenta Clean It, Lavatappeti Portatile, Blu, IN5020sLava Tappezzeria, Divani e Auto, Testine Intercambiabili, Doppio Serba</t>
+          <t>Vacmaster Lavatappeti lava tappezzeria, Ideale per Pulisci Scale, divano, Sedili Auto, Moquette e Tappeti, lava divani e aspi</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DD49JNRL?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DFLYY2H7?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71eADlcR+FL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0DD49JNRL</t>
+          <t>B0DFLYY2H7</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8131,17 +8045,17 @@
       <c r="X19" s="15"/>
       <c r="Y19"/>
       <c r="Z19" s="4">
-        <v>147.53</v>
+        <v>163.93</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="19">
-        <v>1798</v>
+        <v>269</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG19" s="21">
         <v>0</v>
@@ -8193,7 +8107,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0DDKZBYK6</t>
+          <t>B0DJD5C46J</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8206,23 +8120,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Rivenara Lavatappeti Aspirapolvere Tessuti Divani- 450 W Lava Tappezzeria Asciuga e Aspira Acqua Pulitore per Divano Tappeti</t>
+          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DDKZBYK6?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DJD5C46J?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/715qquaM5jL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0DDKZBYK6</t>
+          <t>B0DJD5C46J</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8243,11 +8157,11 @@
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="19">
-        <v>3801</v>
+        <v>338</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG20" s="21">
         <v>0</v>
@@ -8299,7 +8213,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0DFLYY2H7</t>
+          <t>B0DN68M1FK</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8312,23 +8226,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Lavatappeti lava tappezzeria, Ideale per Pulisci Scale, divano, Sedili Auto, Moquette e Tappeti, lava divani e aspi</t>
+          <t>BISSELL PowerWash Compact Pet Lavatappeti e Lava Tappezzeria 600W 4058NsCompatto per macchie di animali e odori, pulitore m</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DFLYY2H7?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DN68M1FK?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61EWFHeeb0L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0DFLYY2H7</t>
+          <t>B0DN68M1FK</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8344,18 +8258,16 @@
       <c r="W21" s="15"/>
       <c r="X21" s="15"/>
       <c r="Y21"/>
-      <c r="Z21" s="4">
-        <v>163.93</v>
-      </c>
+      <c r="Z21" s="4"/>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="19">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG21" s="21">
         <v>0</v>
@@ -8407,7 +8319,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0DJD5C46J</t>
+          <t>B0F54DNT6L</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8420,23 +8332,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
+          <t>Powell Lavatappeti e divani lava e asciuga, lava tappezzeria 450 W, BiancosLavatessuti e smacchiatore portatile per poltron</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DJD5C46J?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F54DNT6L?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/715qquaM5jL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/711kVOskehL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0DJD5C46J</t>
+          <t>B0F54DNT6L</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8457,11 +8369,11 @@
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="19">
-        <v>338</v>
+        <v>528</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="20">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG22" s="21">
         <v>0</v>
@@ -8513,7 +8425,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0DN68M1FK</t>
+          <t>B0F6CWS4ZN</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8526,23 +8438,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>BISSELL PowerWash Compact Pet Lavatappeti e Lava Tappezzeria 600W 4058NsCompatto per macchie di animali e odori, pulitore m</t>
+          <t>BISSELL SpotClean Mini Lavatappeti con Cavo 41491sLava tappezzeria portatile, perfetto per pulizie veloci, compatto e legge</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DN68M1FK?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F6CWS4ZN?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61EWFHeeb0L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0DN68M1FK</t>
+          <t>B0F6CWS4ZN</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8558,16 +8470,18 @@
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
       <c r="Y23"/>
-      <c r="Z23" s="4"/>
+      <c r="Z23" s="4">
+        <v>81.96</v>
+      </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="19">
-        <v>228</v>
+        <v>815</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG23" s="21">
         <v>0</v>
@@ -8619,7 +8533,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0F54DNT6L</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8632,23 +8546,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Powell Lavatappeti e divani lava e asciuga, lava tappezzeria 450 W, BiancosLavatessuti e smacchiatore portatile per poltron</t>
+          <t>Livatro Lavatappeti e Lava Divani, Pulitore per Tappeti,Tessuti e Autos600W, aspirazione da 16kPa, serbatoio da 2,3L e sist</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F54DNT6L?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FH4QL9GN?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/711kVOskehL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0F54DNT6L</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8669,11 +8583,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="19">
-        <v>528</v>
+        <v>257</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="20">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG24" s="21">
         <v>0</v>
@@ -8725,7 +8639,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0F6CWS4ZN</t>
+          <t>B0FHB88T1H</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8738,23 +8652,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean Mini Lavatappeti con Cavo 41491sLava tappezzeria portatile, perfetto per pulizie veloci, compatto e legge</t>
+          <t>Ariete 2482 Spot Cleaner Heat Pro 750W, Pulitore per tappeti e tappezzerie,Lavatappeti, 750W, 2 serbatoi, Nero</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F6CWS4ZN?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FHB88T1H?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61tb8xxsYIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0F6CWS4ZN</t>
+          <t>B0FHB88T1H</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8770,18 +8684,16 @@
       <c r="W25" s="15"/>
       <c r="X25" s="15"/>
       <c r="Y25"/>
-      <c r="Z25" s="4">
-        <v>81.96</v>
-      </c>
+      <c r="Z25" s="4"/>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="19">
-        <v>815</v>
+        <v>86</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="20">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG25" s="21">
         <v>0</v>
@@ -8833,7 +8745,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0FHB8RB8F</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8846,23 +8758,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Livatro Lavatappeti e Lava Divani, Pulitore per Tappeti,Tessuti e Autos600W, aspirazione da 16kPa, serbatoio da 2,3L e sist</t>
+          <t>Cecotec Lavatappeti Aspirapolvere con Cavo Conga 7000 Carpet&amp;Spot Clean Steam. Max. 1700 W, Vapore, Serbatoio Acqua Pulita 16</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FH4QL9GN?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FHB8RB8F?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71uZa1kTCRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0FHB8RB8F</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8883,7 +8795,7 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="19">
-        <v>257</v>
+        <v>95</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="20">
@@ -8939,7 +8851,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FHB88T1H</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8952,23 +8864,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Ariete 2482 Spot Cleaner Heat Pro 750W, Pulitore per tappeti e tappezzerie,Lavatappeti, 750W, 2 serbatoi, Nero</t>
+          <t>Akitas X7 600W Lavatappeti e Divani Lava e Asciuga, 14kPa Potente Aspirazione, Lava Tappezzeria per Auto, Moquette, Materassi</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FHB88T1H?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FJFDG5PY?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tb8xxsYIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FHB88T1H</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -8989,7 +8901,7 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="19">
-        <v>86</v>
+        <v>622</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="20">
@@ -9045,7 +8957,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FHB8RB8F</t>
+          <t>B0FKSTVY4B</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9058,23 +8970,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Lavatappeti Aspirapolvere con Cavo Conga 7000 Carpet&amp;Spot Clean Steam. Max. 1700 W, Vapore, Serbatoio Acqua Pulita 16</t>
+          <t>Livatro Lavatappeti e Pulitore a Vapore 1700 W per Divani, Sofà e AutosVapore a 100 °C pronto in 30 s, aspirazione 15 kPa,</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FHB8RB8F?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FKSTVY4B?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71uZa1kTCRL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FHB8RB8F</t>
+          <t>B0FKSTVY4B</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9090,12 +9002,14 @@
       <c r="W28" s="15"/>
       <c r="X28" s="15"/>
       <c r="Y28"/>
-      <c r="Z28" s="4"/>
+      <c r="Z28" s="4">
+        <v>169.33</v>
+      </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="19">
-        <v>95</v>
+        <v>282</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="20">
@@ -9151,7 +9065,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0FLQ71X9L</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9164,23 +9078,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Akitas X7 600W Lavatappeti e Divani Lava e Asciuga, 14kPa Potente Aspirazione, Lava Tappezzeria per Auto, Moquette, Materassi</t>
+          <t>Rowenta Clean It, Smacchiatore Portatile, Meaning Blue, IN3021scon Auto-Pulizia, Lunga Autonomia, Design Compatto, con Solu</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FJFDG5PY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FLQ71X9L?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71p5IKWpzqL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0FLQ71X9L</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9196,12 +9110,14 @@
       <c r="W29" s="15"/>
       <c r="X29" s="15"/>
       <c r="Y29"/>
-      <c r="Z29" s="4"/>
+      <c r="Z29" s="4">
+        <v>81.96</v>
+      </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="19">
-        <v>622</v>
+        <v>183</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="20">
@@ -9257,7 +9173,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FKSTVY4B</t>
+          <t>B0FMG1PY3G</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9270,23 +9186,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Livatro Lavatappeti e Pulitore a Vapore 1700 W per Divani, Sofà e AutosVapore a 100 °C pronto in 30 s, aspirazione 15 kPa,</t>
+          <t>Olvy Pulitore Tappeti e Divani Lavatappeti Rimuove Macchie Ostinates1 Set | Versione Base | Per Sedili | Aspirazione ad Acq</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FKSTVY4B?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FMG1PY3G?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71nJiB+lf2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FKSTVY4B</t>
+          <t>B0FMG1PY3G</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9302,18 +9218,16 @@
       <c r="W30" s="15"/>
       <c r="X30" s="15"/>
       <c r="Y30"/>
-      <c r="Z30" s="4">
-        <v>169.33</v>
-      </c>
+      <c r="Z30" s="4"/>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="19">
-        <v>282</v>
+        <v>449</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG30" s="21">
         <v>0</v>
@@ -9365,7 +9279,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0FLQ71X9L</t>
+          <t>B0FPGHCD96</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9378,23 +9292,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Rowenta Clean It, Smacchiatore Portatile, Meaning Blue, IN3021scon Auto-Pulizia, Lunga Autonomia, Design Compatto, con Solu</t>
+          <t>KÄRCHER Lavatappeti Smacchiatore SE 2 Spot Care, potenza assorbita: 450 W, serbatoio acqua pulita: 1,5 l, superficie: 2,89 m²</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FLQ71X9L?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FPGHCD96?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71p5IKWpzqL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0FLQ71X9L</t>
+          <t>B0FPGHCD96</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9410,18 +9324,16 @@
       <c r="W31" s="15"/>
       <c r="X31" s="15"/>
       <c r="Y31"/>
-      <c r="Z31" s="4">
-        <v>81.96</v>
-      </c>
+      <c r="Z31" s="4"/>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="19">
-        <v>183</v>
+        <v>551</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG31" s="21">
         <v>0</v>
@@ -9473,7 +9385,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0FMG1PY3G</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9486,23 +9398,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Olvy Pulitore Tappeti e Divani Lavatappeti Rimuove Macchie Ostinates1 Set | Versione Base | Per Sedili | Aspirazione ad Acq</t>
+          <t>LEHMANN EasyWash Lavatappeti Portatile - Aspirapolvere Lava e Asciuga - Sistema a Doppio Serbatoio - Lava Tappezzeria, Tappet</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FMG1PY3G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FS2B5W6P?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71nJiB+lf2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0FMG1PY3G</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9523,11 +9435,11 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="19">
-        <v>449</v>
+        <v>61</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="20">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AG32" s="21">
         <v>0</v>
@@ -9579,7 +9491,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0FPGHCD96</t>
+          <t>B0FXX52XPP</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9592,23 +9504,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER Lavatappeti Smacchiatore SE 2 Spot Care, potenza assorbita: 450 W, serbatoio acqua pulita: 1,5 l, superficie: 2,89 m²</t>
+          <t>Polti StainOver SC20, Lavatappeti a Vapore per Rimuovere le Macchie, 2000 Ws4 in 1, Smacchiatore con Funzione Vaporetto, Te</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FPGHCD96?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FXX52XPP?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51g1W4AC08L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0FPGHCD96</t>
+          <t>B0FXX52XPP</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9629,11 +9541,11 @@
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="19">
-        <v>551</v>
+        <v>12</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" s="21">
         <v>0</v>
@@ -9685,7 +9597,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9698,23 +9610,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN EasyWash Lavatappeti Portatile - Aspirapolvere Lava e Asciuga - Sistema a Doppio Serbatoio - Lava Tappezzeria, Tappet</t>
+          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, legger</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FS2B5W6P?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9735,11 +9647,11 @@
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="19">
-        <v>61</v>
+        <v>220</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="20">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG34" s="21">
         <v>0</v>
@@ -9791,7 +9703,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FXX52XPP</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9804,23 +9716,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Polti StainOver SC20, Lavatappeti a Vapore per Rimuovere le Macchie, 2000 Ws4 in 1, Smacchiatore con Funzione Vaporetto, Te</t>
+          <t>Vacmaster Aspirapolvere Pulitore per tappeti con di riscaldamento 17KpasDispositivo per la pulizia di tappezzeria Ideale pe</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FXX52XPP?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GFKK2WXT?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51g1W4AC08L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FXX52XPP</t>
+          <t>B0GFKK2WXT</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9841,11 +9753,11 @@
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="19">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG35" s="21">
         <v>0</v>
@@ -9897,7 +9809,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9910,23 +9822,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, legger</t>
+          <t>Kitcanis Lavatappeti e Divani Lava e Asciuga 17KPa 600W, Pulitore Tessuti Compatto con 4 Accessori, Serbatoi Rimovibili 1.1L/</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GH6TBJVW?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9947,11 +9859,11 @@
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="19">
-        <v>220</v>
+        <v>91</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG36" s="21">
         <v>0</v>
@@ -10003,7 +9915,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0GK9FV3ZM</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10016,23 +9928,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Aspirapolvere Pulitore per tappeti con di riscaldamento 17KpasDispositivo per la pulizia di tappezzeria Ideale pe</t>
+          <t>BISSELL Little Green Mini Smacchiatore Portatile per Tappeti 41492sPulizia multi-superficie, leggero, con cavo, per tappeti</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GFKK2WXT?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GK9FV3ZM?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GFKK2WXT</t>
+          <t>B0GK9FV3ZM</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10053,11 +9965,11 @@
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="19">
-        <v>34</v>
+        <v>93241</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG37" s="21">
         <v>0</v>
@@ -10109,7 +10021,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0GLNFSYRW</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10122,23 +10034,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Kitcanis Lavatappeti e Divani Lava e Asciuga 17KPa 600W, Pulitore Tessuti Compatto con 4 Accessori, Serbatoi Rimovibili 1.1L/</t>
+          <t>Vozascly F1 Lavatappeti Aspirapolvere Tessuti Divani, Pulitore per Tappeti e Tappezzeria con Aspirazione, 600W+1200W Lava e A</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GH6TBJVW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GLNFSYRW?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/716DCQioXXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0GLNFSYRW</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10159,7 +10071,7 @@
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="19">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="20">
@@ -10215,7 +10127,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GK9FV3ZM</t>
+          <t>B0GQVX8HWW</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10228,23 +10140,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Mini Smacchiatore Portatile per Tappeti 41492sPulizia multi-superficie, leggero, con cavo, per tappeti</t>
+          <t>Rowenta Clean It Hot &amp; Cold, Smacchiatore e Pulitore Portatile, IN7022sper Tappeti e Tessuti, con Due Modalità di Pulizia,</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GK9FV3ZM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GQVX8HWW?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/711kU+bxcYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GK9FV3ZM</t>
+          <t>B0GQVX8HWW</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10260,16 +10172,18 @@
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
       <c r="Y39"/>
-      <c r="Z39" s="4"/>
+      <c r="Z39" s="4">
+        <v>155.73</v>
+      </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="19">
-        <v>93241</v>
+        <v>110</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG39" s="21">
         <v>0</v>
@@ -10321,7 +10235,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GLNFSYRW</t>
+          <t>B0GWJVBKFJ</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10334,23 +10248,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vozascly F1 Lavatappeti Aspirapolvere Tessuti Divani, Pulitore per Tappeti e Tappezzeria con Aspirazione, 600W+1200W Lava e A</t>
+          <t>Rowenta Clean It Hot &amp; Cold, Smacchiatore 3 in 1, IN7021sTecnologia PowerHeat, Pulizia a Caldo e Freddo, Per Tappeti, Divan</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GLNFSYRW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GWJVBKFJ?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/716DCQioXXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/714vNMrXVYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GLNFSYRW</t>
+          <t>B0GWJVBKFJ</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10371,11 +10285,11 @@
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="19">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="20">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AG40" s="21">
         <v>0</v>
@@ -10427,7 +10341,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GQVX8HWW</t>
+          <t>B0H1B164KH</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10440,23 +10354,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Rowenta Clean It Hot &amp; Cold, Smacchiatore e Pulitore Portatile, IN7022sper Tappeti e Tessuti, con Due Modalità di Pulizia,</t>
+          <t>Uwant Y100S Lavatappeti Vapore Lava e Asciuga, 1750W 18kPa, 2.4L SerbatoiosTubo con Auto-pulizia, Spazzola 2in1 Ribaltabile</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GQVX8HWW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H1B164KH?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/711kU+bxcYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GQVX8HWW</t>
+          <t>B0H1B164KH</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10472,18 +10386,16 @@
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
       <c r="Y41"/>
-      <c r="Z41" s="4">
-        <v>155.73</v>
-      </c>
+      <c r="Z41" s="4"/>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="19">
-        <v>110</v>
+        <v>440</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG41" s="21">
         <v>0</v>
@@ -10535,7 +10447,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0GWJVBKFJ</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10548,23 +10460,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Rowenta Clean It Hot &amp; Cold, Smacchiatore 3 in 1, IN7021sTecnologia PowerHeat, Pulizia a Caldo e Freddo, Per Tappeti, Divan</t>
+          <t>Hearten Lavatappeti Portatile, Aspirazione da 22kPa, con Auto-PuliziasLava Tappezzeria, 1.5L Serbatoio, Design Compatto, Ac</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GWJVBKFJ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H263J8GJ?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/714vNMrXVYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0GWJVBKFJ</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10585,11 +10497,11 @@
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG42" s="21">
         <v>0</v>
@@ -10641,7 +10553,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H1B164KH</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10654,23 +10566,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100S Lavatappeti Vapore Lava e Asciuga, 1750W 18kPa, 2.4L SerbatoiosTubo con Auto-pulizia, Spazzola 2in1 Ribaltabile</t>
+          <t>LEHMANN SteamWash 1800 Lavatappezzeria e Pulitore a Vapore 4 in 1, Lavatappeti e Divani con Acqua Calda 60°C e Vapore 116°C,</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H1B164KH?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H3LCDNGF?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H1B164KH</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10691,11 +10603,11 @@
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="19">
-        <v>440</v>
+        <v>36</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="20">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG43" s="21">
         <v>0</v>
@@ -10747,7 +10659,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10760,23 +10672,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Hearten Lavatappeti Portatile, Aspirazione da 22kPa, con Auto-PuliziasLava Tappezzeria, 1.5L Serbatoio, Design Compatto, Ac</t>
+          <t>Redkey Rd-F1 Lavatappeti Lava e Asciuga, 4 in 1 Aspiratore Lava a Vapore con Aspirazione 26000Pa, 1800W Pulizia Profonda per</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H263J8GJ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H4TXR27S?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10797,11 +10709,11 @@
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="20">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AG44" s="21">
         <v>0</v>
@@ -10853,7 +10765,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0H5L383SW</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10866,23 +10778,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN SteamWash 1800 Lavatappezzeria e Pulitore a Vapore 4 in 1, Lavatappeti e Divani con Acqua Calda 60°C e Vapore 116°C,</t>
+          <t>Livatro Lavatappeti e Pulitore a Vapore 2100 W per Divani, Sofà e AutosVapore a 100 °C pronto in 30 s, aspirazione 18 kPa,</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H3LCDNGF?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H5L383SW?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0H5L383SW</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10903,11 +10815,11 @@
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="19">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG45" s="21">
         <v>0</v>
@@ -10959,7 +10871,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
+          <t>B0H944DVN4</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -10972,23 +10884,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Redkey Rd-F1 Lavatappeti Lava e Asciuga, 4 in 1 Aspiratore Lava a Vapore con Aspirazione 26000Pa, 1800W Pulizia Profonda per</t>
+          <t>BISSELL SpotClean C9 pulitore di macchie portatile 3911NsPulitore per rivestimenti tappezzeria portatile, pulitore per macc</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H4TXR27S?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H944DVN4?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71P3Xf6oErL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
+          <t>B0H944DVN4</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11004,16 +10916,18 @@
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46"/>
-      <c r="Z46" s="4"/>
+      <c r="Z46" s="4">
+        <v>163.93</v>
+      </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="19">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="20">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AG46" s="21">
         <v>0</v>
@@ -11065,7 +10979,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H5L383SW</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11078,23 +10992,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Livatro Lavatappeti e Pulitore a Vapore 2100 W per Divani, Sofà e AutosVapore a 100 °C pronto in 30 s, aspirazione 18 kPa,</t>
+          <t>PUREBEAR Pulitore Tappezzeria, Lavatappeti Divani LavasLavatappeti Divani Lava | Tubo Lungo Pulizia Divano| Materasso| Sedi</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H5L383SW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H97LW9DL?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71hXCEHucsL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H5L383SW</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11115,11 +11029,11 @@
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="19">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="20">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AG47" s="21">
         <v>0</v>
@@ -11171,7 +11085,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H944DVN4</t>
+          <t>B0HBWJY7M3</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11184,23 +11098,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean C9 pulitore di macchie portatile 3911NsPulitore per rivestimenti tappezzeria portatile, pulitore per macc</t>
+          <t>Vacmaster 16Kpa Lavatessuti e LavateppetisSmacchiatore Auto &amp; Divani 500W | Spotlet pulisce come lavatessuti portatile tepp</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H944DVN4?psc=1</t>
+          <t>https://www.amazon.it/dp/B0HBWJY7M3?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71P3Xf6oErL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71lBEXdUO8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H944DVN4</t>
+          <t>B0HBWJY7M3</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11217,17 +11131,17 @@
       <c r="X48" s="15"/>
       <c r="Y48"/>
       <c r="Z48" s="4">
-        <v>163.93</v>
+        <v>65.57</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="19">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="20">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AG48" s="21">
         <v>0</v>
@@ -11279,7 +11193,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H97LW9DL</t>
+          <t>B0HCN3FWXH</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11292,23 +11206,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>PUREBEAR Pulitore Tappezzeria, Lavatappeti Divani LavasLavatappeti Divani Lava | Tubo Lungo Pulizia Divano| Materasso| Sedi</t>
+          <t>TWOPOINT lava tappezzeria Potente aspirazione da 15 kPasPulizia profonda in 3 fasi, design leggero e portatile di soli 3,8</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H97LW9DL?psc=1</t>
+          <t>https://www.amazon.it/dp/B0HCN3FWXH?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71hXCEHucsL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H97LW9DL</t>
+          <t>B0HCN3FWXH</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11329,11 +11243,11 @@
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="19">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG49" s="21">
         <v>0</v>
@@ -11378,476 +11292,252 @@
       <c r="BQ49" s="22"/>
       <c r="BR49"/>
     </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0HBWJY7M3</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>Vacmaster 16Kpa Lavatessuti e LavateppetisSmacchiatore Auto &amp; Divani 500W | Spotlet pulisce come lavatessuti portatile tepp</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0HBWJY7M3?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71lBEXdUO8L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0HBWJY7M3</t>
-        </is>
-      </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50"/>
-      <c r="Z50" s="4">
-        <v>65.57</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE50"/>
-      <c r="AF50" s="20">
-        <v>5</v>
-      </c>
-      <c r="AG50" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH50"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="19"/>
-      <c r="AM50"/>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
-      <c r="BK50" s="22"/>
-      <c r="BL50"/>
-      <c r="BM50" s="22"/>
-      <c r="BN50"/>
-      <c r="BO50" s="22"/>
-      <c r="BP50"/>
-      <c r="BQ50" s="22"/>
-      <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HCN3FWXH</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>TWOPOINT lava tappezzeria Potente aspirazione da 15 kPasPulizia profonda in 3 fasi, design leggero e portatile di soli 3,8</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0HCN3FWXH?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HCN3FWXH</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="19">
-        <v>7</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="20">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="22"/>
-      <c r="BL51"/>
-      <c r="BM51" s="22"/>
-      <c r="BN51"/>
-      <c r="BO51" s="22"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="22"/>
-      <c r="BR51"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.it/dp/B07GXS35PG"/>
     <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.it/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51L21EY2IeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.it/dp/B07GXS35PG"/>
+    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.it/dp/B07GXS35PG?psc=1"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PEgi0LW+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.it/dp/B07GXS35PG"/>
+    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.it/dp/B084PSXMQM"/>
     <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.it/dp/B07GXS35PG?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PEgi0LW+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.it/dp/B07GXS35PG"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.it/dp/B084PSXMQM"/>
+    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.it/dp/B084PSXMQM?psc=1"/>
+    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.it/dp/B084PSXMQM"/>
+    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.it/dp/B0B3J3Q9RD"/>
     <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.it/dp/B084PSXMQM?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717n80vcVUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.it/dp/B084PSXMQM"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
+    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.it/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.it/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.it/dp/B0BMF3LFC8"/>
     <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.it/dp/B086Q46MMD?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61sF4ZQ-2cL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.it/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.it/dp/B0BMF3LFC8?psc=1"/>
+    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.it/dp/B0BMF3LFC8"/>
+    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
     <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.it/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.it/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.it/dp/B0BMF3LFC8"/>
+    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
+    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lbQJ889kL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.it/dp/B0BS13X4Z2"/>
     <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.it/dp/B0BMF3LFC8?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.it/dp/B0BMF3LFC8"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
+    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.it/dp/B0BS13X4Z2?psc=1"/>
+    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.it/dp/B0BS13X4Z2"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lbQJ889kL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.it/dp/B0BS13X4Z2"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.it/dp/B0BS13X4Z2?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71o8bjO+qpL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.it/dp/B0BS13X4Z2"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.it/dp/B0CM6TD52F?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71csw3LJPeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.it/dp/B0CW9VBM8R"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.it/dp/B0CW9VBM8R?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FFs6EAy4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.it/dp/B0CW9VBM8R"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.it/dp/B0CXJLJQD1"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.it/dp/B0CM6TD52F?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71csw3LJPeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.it/dp/B0CW9VBM8R"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.it/dp/B0CXJLJQD1?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61MZMklEU5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.it/dp/B0CXJLJQD1"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.it/dp/B0CXMC73YV"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.it/dp/B0CW9VBM8R?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FFs6EAy4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.it/dp/B0CW9VBM8R"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.it/dp/B0CXJLJQD1"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.it/dp/B0CXMC73YV?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71sPYtqS0TL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.it/dp/B0CXMC73YV"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.it/dp/B0CXJLJQD1?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61MZMklEU5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.it/dp/B0CXJLJQD1"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.it/dp/B0CXMC73YV"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.it/dp/B0D2HFLM1C?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.it/dp/B0D6YR6562"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.it/dp/B0CXMC73YV?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71sPYtqS0TL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.it/dp/B0CXMC73YV"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.it/dp/B0D6YR6562?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TZUWy-CyL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.it/dp/B0D6YR6562"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.it/dp/B0D2HFLM1C?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.it/dp/B0D6YR6562"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.it/dp/B0D8KZDB13?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xvnovCAAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.it/dp/B0DBLD211L"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.it/dp/B0D6YR6562?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TZUWy-CyL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.it/dp/B0D6YR6562"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.it/dp/B0DBLD211L?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61v4meZXpjL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.it/dp/B0DBLD211L"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.it/dp/B0DD49JNRL"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.it/dp/B0D8KZDB13?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xvnovCAAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.it/dp/B0DBLD211L"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.it/dp/B0DD49JNRL?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71eADlcR+FL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.it/dp/B0DD49JNRL"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.it/dp/B0DDKZBYK6"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.it/dp/B0DBLD211L?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61v4meZXpjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.it/dp/B0DBLD211L"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.it/dp/B0DD49JNRL"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.it/dp/B0DDKZBYK6?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.it/dp/B0DDKZBYK6"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.it/dp/B0DD49JNRL?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71eADlcR+FL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.it/dp/B0DD49JNRL"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.it/dp/B0DDKZBYK6"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.it/dp/B0DFLYY2H7?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.it/dp/B0DDKZBYK6?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.it/dp/B0DDKZBYK6"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.it/dp/B0DJD5C46J?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/715qquaM5jL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.it/dp/B0DN68M1FK"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.it/dp/B0DFLYY2H7?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7154Sj-lWDL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.it/dp/B0DN68M1FK?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61EWFHeeb0L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.it/dp/B0DN68M1FK"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.it/dp/B0F54DNT6L"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.it/dp/B0DJD5C46J?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/715qquaM5jL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.it/dp/B0DN68M1FK"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.it/dp/B0F54DNT6L?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711kVOskehL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.it/dp/B0F54DNT6L"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.it/dp/B0F6CWS4ZN"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.it/dp/B0DN68M1FK?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61EWFHeeb0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.it/dp/B0DN68M1FK"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.it/dp/B0F54DNT6L"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.it/dp/B0F6CWS4ZN?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.it/dp/B0F6CWS4ZN"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.it/dp/B0FH4QL9GN"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.it/dp/B0F54DNT6L?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711kVOskehL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.it/dp/B0F54DNT6L"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.it/dp/B0F6CWS4ZN"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.it/dp/B0FH4QL9GN?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.it/dp/B0FH4QL9GN"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.it/dp/B0FHB88T1H"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.it/dp/B0F6CWS4ZN?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.it/dp/B0F6CWS4ZN"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.it/dp/B0FH4QL9GN"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.it/dp/B0FHB88T1H?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tb8xxsYIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.it/dp/B0FHB88T1H"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.it/dp/B0FH4QL9GN?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nARwekliL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.it/dp/B0FH4QL9GN"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.it/dp/B0FHB88T1H"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.it/dp/B0FHB8RB8F?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71uZa1kTCRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.it/dp/B0FHB88T1H?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tb8xxsYIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.it/dp/B0FHB88T1H"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.it/dp/B0FJFDG5PY?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.it/dp/B0FKSTVY4B"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.it/dp/B0FHB8RB8F?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71uZa1kTCRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.it/dp/B0FKSTVY4B?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.it/dp/B0FKSTVY4B"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.it/dp/B0FLQ71X9L"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.it/dp/B0FJFDG5PY?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71XUjnFFERL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.it/dp/B0FKSTVY4B"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.it/dp/B0FLQ71X9L?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71p5IKWpzqL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.it/dp/B0FLQ71X9L"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.it/dp/B0FMG1PY3G"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.it/dp/B0FKSTVY4B?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61vNLxoQL3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.it/dp/B0FKSTVY4B"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.it/dp/B0FLQ71X9L"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.it/dp/B0FMG1PY3G?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nJiB+lf2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.it/dp/B0FMG1PY3G"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.it/dp/B0FPGHCD96"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.it/dp/B0FLQ71X9L?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71p5IKWpzqL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.it/dp/B0FLQ71X9L"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.it/dp/B0FMG1PY3G"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.it/dp/B0FPGHCD96?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.it/dp/B0FPGHCD96"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.it/dp/B0FS2B5W6P"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.it/dp/B0FMG1PY3G?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71nJiB+lf2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.it/dp/B0FMG1PY3G"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.it/dp/B0FPGHCD96"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.it/dp/B0FS2B5W6P?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.it/dp/B0FS2B5W6P"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.it/dp/B0FPGHCD96?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.it/dp/B0FPGHCD96"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.it/dp/B0FS2B5W6P"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.it/dp/B0FXX52XPP?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51g1W4AC08L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.it/dp/B0FS2B5W6P?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.it/dp/B0FS2B5W6P"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.it/dp/B0GFKK2WXT"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.it/dp/B0FXX52XPP?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51g1W4AC08L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.it/dp/B0GFKK2WXT?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.it/dp/B0GFKK2WXT"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.it/dp/B0GFKK2WXT"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.it/dp/B0GH6TBJVW?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.it/dp/B0GK9FV3ZM"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.it/dp/B0GFKK2WXT?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xLT6M5eiL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.it/dp/B0GFKK2WXT"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.it/dp/B0GK9FV3ZM?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.it/dp/B0GK9FV3ZM"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.it/dp/B0GH6TBJVW?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71j7k36yP8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.it/dp/B0GK9FV3ZM"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.it/dp/B0GLNFSYRW?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/716DCQioXXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.it/dp/B0GQVX8HWW"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.it/dp/B0GK9FV3ZM?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6127eJoRLkL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.it/dp/B0GK9FV3ZM"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.it/dp/B0GQVX8HWW?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711kU+bxcYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.it/dp/B0GQVX8HWW"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.it/dp/B0GWJVBKFJ"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.it/dp/B0GLNFSYRW?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/716DCQioXXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.it/dp/B0GQVX8HWW"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.it/dp/B0GWJVBKFJ?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/714vNMrXVYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.it/dp/B0GWJVBKFJ"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.it/dp/B0H1B164KH"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.it/dp/B0GQVX8HWW?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711kU+bxcYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.it/dp/B0GQVX8HWW"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.it/dp/B0GWJVBKFJ"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.it/dp/B0H1B164KH?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.it/dp/B0H1B164KH"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.it/dp/B0GWJVBKFJ?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/714vNMrXVYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.it/dp/B0GWJVBKFJ"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.it/dp/B0H1B164KH"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.it/dp/B0H263J8GJ?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.it/dp/B0H1B164KH?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.it/dp/B0H1B164KH"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.it/dp/B0H3LCDNGF?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.it/dp/B0H263J8GJ?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.it/dp/B0H4TXR27S?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.it/dp/B0H5L383SW"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.it/dp/B0H3LCDNGF?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71dXYMBsbnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.it/dp/B0H5L383SW?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.it/dp/B0H5L383SW"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.it/dp/B0H944DVN4"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.it/dp/B0H4TXR27S?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81Jkh0tTERL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.it/dp/B0H5L383SW"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.it/dp/B0H944DVN4?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71P3Xf6oErL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.it/dp/B0H944DVN4"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.it/dp/B0H5L383SW?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+mMhtp+hL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.it/dp/B0H5L383SW"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.it/dp/B0H944DVN4"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.it/dp/B0H97LW9DL?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71hXCEHucsL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.it/dp/B0H944DVN4?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71P3Xf6oErL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.it/dp/B0H944DVN4"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.it/dp/B0HBWJY7M3?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71lBEXdUO8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.it/dp/B0HCN3FWXH"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.it/dp/B0H97LW9DL?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71hXCEHucsL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
-    <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.it/dp/B0HBWJY7M3?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71lBEXdUO8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.it/dp/B0HCN3FWXH"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.it/dp/B0HCN3FWXH?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.it/dp/B0HCN3FWXH"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.it/dp/B0HCN3FWXH?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Xqa1xYofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.it/dp/B0HCN3FWXH"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId241"/>
 </worksheet>
 </file>
 
